--- a/Daily Sales Forecasting Methodology/2026 festive feature.xlsx
+++ b/Daily Sales Forecasting Methodology/2026 festive feature.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\G0004878\Desktop\TFT_Data\Daily_forecasting_model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\G0004878\Desktop\TFT_Data\Temporal-Fusion-Transformers-Material\Daily Sales Forecasting Methodology\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -159,6 +159,27 @@
   </si>
   <si>
     <t>D+6</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>C+1</t>
+  </si>
+  <si>
+    <t>C+2</t>
+  </si>
+  <si>
+    <t>C+3</t>
+  </si>
+  <si>
+    <t>C+4</t>
+  </si>
+  <si>
+    <t>C+5</t>
+  </si>
+  <si>
+    <t>C+6</t>
   </si>
 </sst>
 </file>
@@ -478,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AR274"/>
+  <dimension ref="A1:AY274"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -500,7 +521,7 @@
     <col min="38" max="41" width="4.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -633,23 +654,44 @@
       <c r="AR1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.35">
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>46266</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>46267</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>46268</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>46269</v>
       </c>
@@ -657,47 +699,47 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>46270</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>46271</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>46272</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>46273</v>
       </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>46274</v>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>46275</v>
       </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>46276</v>
       </c>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>46277</v>
       </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>46278</v>
       </c>
@@ -705,7 +747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>46279</v>
       </c>
@@ -713,7 +755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>46280</v>
       </c>
@@ -3335,86 +3377,107 @@
       </c>
       <c r="L112" s="1"/>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>46377</v>
       </c>
       <c r="M113" s="1"/>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>46378</v>
       </c>
       <c r="N114" s="1"/>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>46379</v>
       </c>
       <c r="O115" s="1"/>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>46380</v>
       </c>
       <c r="P116" s="1"/>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>46381</v>
       </c>
       <c r="Q117" s="1"/>
-    </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="AS117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>46382</v>
       </c>
       <c r="R118" s="1"/>
-    </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="AT118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>46383</v>
       </c>
       <c r="S119" s="1"/>
-    </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="AU119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>46384</v>
       </c>
       <c r="T120" s="1"/>
-    </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="AV120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>46385</v>
       </c>
       <c r="U121" s="1"/>
-    </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="AW121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>46386</v>
       </c>
       <c r="V122" s="1"/>
-    </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="AX122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>46387</v>
       </c>
       <c r="W123" s="1"/>
-    </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="AY123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A124" s="2"/>
       <c r="X124" s="1"/>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A125" s="2"/>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A126" s="2"/>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A127" s="2"/>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A128" s="2"/>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.35">
